--- a/smartshop/EvidenceBasedAdaptiveUI/reports/PersonalityNudges/trait_modifiers.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/PersonalityNudges/trait_modifiers.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         <v>-1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.323285</v>
+        <v>0.313547</v>
       </c>
     </row>
     <row r="3">
@@ -500,7 +500,7 @@
         <v>-1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.606754</v>
+        <v>0.626089</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>-1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.606754</v>
+        <v>0.626089</v>
       </c>
     </row>
     <row r="5">
@@ -534,7 +534,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -546,30 +546,30 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.633345</v>
+        <v>0.30661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>recommendation_strength</t>
+          <t>whitespace</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.326507</v>
+        <v>0.557937</v>
       </c>
     </row>
     <row r="7">
@@ -592,7 +592,7 @@
         <v>-1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.258723</v>
+        <v>0.557937</v>
       </c>
     </row>
     <row r="8">
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.272673</v>
+        <v>0.319887</v>
       </c>
     </row>
     <row r="9">
@@ -626,7 +626,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.487196</v>
+        <v>0.816638</v>
       </c>
     </row>
     <row r="10">
@@ -654,14 +654,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>recommendation_strength</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.487196</v>
+        <v>0.496822</v>
       </c>
     </row>
     <row r="11">
@@ -677,37 +677,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>whitespace</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.487196</v>
+        <v>0.496822</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>whitespace</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.556878</v>
+        <v>0.496822</v>
       </c>
     </row>
     <row r="13">
@@ -723,14 +723,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.556878</v>
+        <v>0.521064</v>
       </c>
     </row>
     <row r="14">
@@ -741,7 +741,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -750,10 +750,33 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.521064</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Openness</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>visual_richness</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.405088</v>
+      <c r="E15" t="n">
+        <v>0.408289</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,7 +900,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.326507</v>
+        <v>0.30661</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -885,38 +908,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.13587</v>
+        <v>0.097985</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13503</v>
+        <v>0.122641</v>
       </c>
       <c r="N2" t="n">
-        <v>0.018411</v>
+        <v>0.025799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>recommendation_strength</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>recommendation_emphasis</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -929,31 +952,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>data-driven</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.633345</v>
+        <v>0.319887</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.13587</v>
+        <v>0.109735</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13503</v>
+        <v>0.138486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.018411</v>
+        <v>0.02673</v>
       </c>
     </row>
     <row r="4">
@@ -964,52 +985,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>whitespace</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>whitespace</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>decrease</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>data-driven</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.272673</v>
+        <v>0.807238</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.057</v>
+      </c>
       <c r="L4" t="n">
-        <v>0.067581</v>
+        <v>0.174924</v>
       </c>
       <c r="M4" t="n">
-        <v>0.136669</v>
+        <v>0.163429</v>
       </c>
       <c r="N4" t="n">
-        <v>0.027815</v>
+        <v>0.037647</v>
       </c>
     </row>
     <row r="5">
@@ -1047,25 +1070,25 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.258723</v>
+        <v>0.308637</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.067581</v>
+        <v>0.109735</v>
       </c>
       <c r="M5" t="n">
-        <v>0.136669</v>
+        <v>0.138486</v>
       </c>
       <c r="N5" t="n">
-        <v>0.027815</v>
+        <v>0.02673</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1126,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.635308</v>
+        <v>0.649328</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1111,19 +1134,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0723</v>
+        <v>-0.0793</v>
       </c>
       <c r="L6" t="n">
-        <v>0.147525</v>
+        <v>0.134106</v>
       </c>
       <c r="M6" t="n">
-        <v>0.118417</v>
+        <v>0.127419</v>
       </c>
       <c r="N6" t="n">
-        <v>0.025219</v>
+        <v>0.018839</v>
       </c>
     </row>
     <row r="7">
@@ -1161,7 +1184,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5782</v>
+        <v>0.602851</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1169,19 +1192,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0522</v>
+        <v>-0.0616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.092127</v>
+        <v>0.106715</v>
       </c>
       <c r="M7" t="n">
-        <v>0.149454</v>
+        <v>0.137781</v>
       </c>
       <c r="N7" t="n">
-        <v>0.029968</v>
+        <v>0.023054</v>
       </c>
     </row>
     <row r="8">
@@ -1219,7 +1242,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.01305</v>
+        <v>0.01485</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1227,7 +1250,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
@@ -1275,7 +1298,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.323285</v>
+        <v>0.313547</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1283,17 +1306,17 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.147525</v>
+        <v>0.134106</v>
       </c>
       <c r="M9" t="n">
-        <v>0.118417</v>
+        <v>0.127419</v>
       </c>
       <c r="N9" t="n">
-        <v>0.025219</v>
+        <v>0.018839</v>
       </c>
     </row>
     <row r="10">
@@ -1331,7 +1354,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.765863</v>
+        <v>0.792847</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1339,19 +1362,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0503</v>
+        <v>0.0528</v>
       </c>
       <c r="L10" t="n">
-        <v>0.19336</v>
+        <v>0.179644</v>
       </c>
       <c r="M10" t="n">
-        <v>0.160564</v>
+        <v>0.151059</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03152</v>
+        <v>0.037582</v>
       </c>
     </row>
     <row r="11">
@@ -1389,7 +1412,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.361396</v>
+        <v>0.368946</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1397,17 +1420,17 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.130845</v>
+        <v>0.122399</v>
       </c>
       <c r="M11" t="n">
-        <v>0.159458</v>
+        <v>0.175576</v>
       </c>
       <c r="N11" t="n">
-        <v>0.036613</v>
+        <v>0.032592</v>
       </c>
     </row>
     <row r="12">
@@ -1445,7 +1468,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.33433</v>
+        <v>0.328673</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1453,17 +1476,17 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.104545</v>
+        <v>0.09604600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.173464</v>
+        <v>0.159441</v>
       </c>
       <c r="N12" t="n">
-        <v>0.030008</v>
+        <v>0.032268</v>
       </c>
     </row>
     <row r="13">
@@ -1501,7 +1524,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.02025</v>
+        <v>0.0216</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1509,7 +1532,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1525,57 +1548,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>recommendation_strength</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>recommendation_emphasis</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>decrease</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>data-driven</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.405088</v>
+        <v>0.816638</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>59</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.0515</v>
+      </c>
       <c r="L14" t="n">
-        <v>0.174994</v>
+        <v>0.179644</v>
       </c>
       <c r="M14" t="n">
-        <v>0.145288</v>
+        <v>0.151059</v>
       </c>
       <c r="N14" t="n">
-        <v>0.040455</v>
+        <v>0.037582</v>
       </c>
     </row>
     <row r="15">
@@ -1591,12 +1616,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>animation</t>
+          <t>visual_richness</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>animation_level</t>
+          <t>visual_richness</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1613,25 +1638,25 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.02655</v>
+        <v>0.408289</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.184476</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.147466</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.031123</v>
       </c>
     </row>
     <row r="16">
@@ -1642,17 +1667,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>animation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>animation_level</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1665,31 +1690,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>data-driven</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.720818</v>
+        <v>0.0279</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Very Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.09</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.13946</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.163294</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.025649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1705,47 +1728,49 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>decrease</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>data-driven</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.392938</v>
+        <v>0.645089</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0566</v>
+      </c>
       <c r="L17" t="n">
-        <v>0.174994</v>
+        <v>0.141341</v>
       </c>
       <c r="M17" t="n">
-        <v>0.145288</v>
+        <v>0.14311</v>
       </c>
       <c r="N17" t="n">
-        <v>0.040455</v>
+        <v>0.019238</v>
       </c>
     </row>
     <row r="18">
@@ -1761,12 +1786,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>animation</t>
+          <t>visual_richness</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>animation_level</t>
+          <t>visual_richness</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1783,24 +1808,80 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.0144</v>
+        <v>0.397039</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
+        <v>0.184476</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.147466</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.031123</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Openness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>animation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>animation_level</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>decrease</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>theory</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01665</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>37</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1815,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,13 +1977,13 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7275</v>
+        <v>0.7232</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7287</v>
+        <v>0.7197</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1913,17 +1994,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>recommendation_emphasis</t>
+          <t>information_density</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1934,21 +2015,19 @@
           <t>increase</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7275</v>
+        <v>0.5312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8125</v>
+        <v>0.5221</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>data-driven</t>
+          <t>theory</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2039,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1969,22 +2048,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>decrease</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H4" t="n">
-        <v>0.535</v>
+        <v>0.5312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5465</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2005,7 +2084,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>whitespace</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2016,19 +2095,21 @@
           <t>decrease</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>-0.057</v>
+      </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.535</v>
+        <v>0.5454</v>
       </c>
       <c r="I5" t="n">
-        <v>0.55</v>
+        <v>0.4884</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>data-driven</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2139,7 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -2093,16 +2174,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-0.0522</v>
+        <v>-0.0616</v>
       </c>
       <c r="G7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>0.535</v>
+        <v>0.5312</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4828</v>
+        <v>0.4697</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2135,16 +2216,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-0.0723</v>
+        <v>-0.0793</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7275</v>
+        <v>0.7232</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6552</v>
+        <v>0.6439</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2178,13 +2259,13 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7275</v>
+        <v>0.7232</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7131</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2218,7 +2299,7 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -2254,13 +2335,13 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>0.535</v>
+        <v>0.5312</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5556</v>
+        <v>0.5573</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2293,16 +2374,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.0503</v>
+        <v>0.0528</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7275</v>
+        <v>0.7232</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7778</v>
+        <v>0.776</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -2336,13 +2417,13 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5558</v>
+        <v>0.5454</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5333</v>
+        <v>0.5278</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -2353,36 +2434,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>animation_level</t>
+          <t>recommendation_emphasis</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>increase</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>decrease</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.0515</v>
+      </c>
       <c r="G14" t="n">
-        <v>59</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7232</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6717</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>data-driven</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>visual_richness</t>
+          <t>animation_level</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2412,14 +2499,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>59</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6072</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6111</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>theory</t>
@@ -2434,28 +2517,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>animation_level</t>
+          <t>visual_richness</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>decrease</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>32</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6062</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6138</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>theory</t>
@@ -2475,32 +2562,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>information_density</t>
+          <t>animation_level</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>increase</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.09</v>
-      </c>
+          <t>decrease</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>32</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.625</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>data-driven</t>
+          <t>theory</t>
         </is>
       </c>
     </row>
@@ -2517,28 +2598,70 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>information_density</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>increase</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="G18" t="n">
+        <v>37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>data-driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Openness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>visual_richness</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>decrease</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>32</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6072</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.6042</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>37</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6062</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>theory</t>
         </is>
